--- a/MainTop/08.05.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/08.05.2026 Таня Озон/print_print_sorted.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\08.05.2026 Таня Озон\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\08.05.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC947117-63A8-4513-9FA8-97E07A48BF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401D44D4-121C-4F9A-8E70-12CF24188449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,6 +589,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="8">
@@ -662,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -673,6 +675,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -996,50 +1001,50 @@
     <col min="19" max="19" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="135" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
